--- a/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/continuation/conductor_diagnostic.xlsx
+++ b/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/continuation/conductor_diagnostic.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spatial_distribution" sheetId="1" r:id="R0644bc5712344872"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time_evolution" sheetId="2" r:id="R86064da6de8c4e09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spatial_distribution" sheetId="1" r:id="R0096176808a64972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time_evolution" sheetId="2" r:id="Rd5a3ffffe8cd43d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -382,7 +382,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>time to plot spatial dustribution of the solution </x:v>
+        <x:v>Time at which the spatial distribution of the solution is plotted.</x:v>
       </x:c>
       <x:c r="E4" s="10" t="n">
         <x:v>610</x:v>
